--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort5.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort5.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C76FB2F-3FEB-4FB2-A366-76D077A5E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6868C05-3B2E-4929-BDE8-3E351EA9F135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B219D52F-6A30-4819-951B-0A0090036AA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B219D52F-6A30-4819-951B-0A0090036AA5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Weight" sheetId="1" r:id="rId1"/>
+    <sheet name="GTT" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="17">
   <si>
     <t>Mice</t>
   </si>
@@ -81,6 +82,15 @@
   </si>
   <si>
     <t>1855M5</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Glycemia (mg.dl)</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -1272,4 +1282,532 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A7B3DB-0E1C-444B-8733-18964E56C78A}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>162</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>290</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>500</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>440</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>331</v>
+      </c>
+      <c r="D6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>238</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>174</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>348</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>473</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>364</v>
+      </c>
+      <c r="D11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>264</v>
+      </c>
+      <c r="D12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>228</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>138</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>400</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>464</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>268</v>
+      </c>
+      <c r="D17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>243</v>
+      </c>
+      <c r="D18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>181</v>
+      </c>
+      <c r="D19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>137</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>367</v>
+      </c>
+      <c r="D21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>402</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>292</v>
+      </c>
+      <c r="D23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>229</v>
+      </c>
+      <c r="D24">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>179</v>
+      </c>
+      <c r="D25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>114</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>326</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>390</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>286</v>
+      </c>
+      <c r="D29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>176</v>
+      </c>
+      <c r="D30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>158</v>
+      </c>
+      <c r="D31">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>210</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>355</v>
+      </c>
+      <c r="D33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>355</v>
+      </c>
+      <c r="D34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>273</v>
+      </c>
+      <c r="D35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>183</v>
+      </c>
+      <c r="D36">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>194</v>
+      </c>
+      <c r="D37">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>